--- a/1日めの復習/himiz.xlsx
+++ b/1日めの復習/himiz.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Sheet1!$A$1:$G$23</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -96,6 +99,7 @@
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -133,7 +137,7 @@
     <font>
       <sz val="12"/>
       <name val="Noto Serif CJK JP"/>
-      <family val="1"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -256,19 +260,19 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>90000</xdr:colOff>
+      <xdr:colOff>277560</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:rowOff>18720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="0" name="テキスト枠 1"/>
-        <xdr:cNvSpPr txBox="1"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="304920" y="1989000"/>
-          <a:ext cx="2904120" cy="1606320"/>
+          <a:ext cx="3091680" cy="1605960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -280,11 +284,22 @@
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif CJK JP"/>
@@ -296,11 +311,16 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-              <a:latin typeface="Noto Serif CJK JP"/>
-            </a:rPr>
-            <a:t>ID     INT</a:t>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>ID         INT</a:t>
           </a:r>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
@@ -313,11 +333,16 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
-              <a:latin typeface="Noto Serif CJK JP"/>
-            </a:rPr>
-            <a:t>名前 </a:t>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>名前     </a:t>
           </a:r>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
@@ -342,11 +367,16 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
-              <a:latin typeface="Noto Serif CJK JP"/>
-            </a:rPr>
-            <a:t>性別 </a:t>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>性別     </a:t>
           </a:r>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
@@ -395,6 +425,11 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif CJK JP"/>
@@ -418,11 +453,16 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
-              <a:latin typeface="Noto Serif CJK JP"/>
-            </a:rPr>
-            <a:t>出身 </a:t>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif CJK JP"/>
+            </a:rPr>
+            <a:t>出身     </a:t>
           </a:r>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
@@ -573,7 +613,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.78"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
